--- a/artfynd/A 10370-2026 artfynd.xlsx
+++ b/artfynd/A 10370-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130175782</v>
+        <v>130175780</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Genmyran, Kultsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518218</v>
+        <v>518227</v>
       </c>
       <c r="R2" t="n">
-        <v>7206465</v>
+        <v>7206436</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,32 +797,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130175794</v>
+        <v>130175784</v>
       </c>
       <c r="B3" t="n">
-        <v>83057</v>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518300</v>
+        <v>518236</v>
       </c>
       <c r="R3" t="n">
-        <v>7206131</v>
+        <v>7206497</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +907,7 @@
         <v>130175791</v>
       </c>
       <c r="B4" t="n">
-        <v>92059</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130175780</v>
+        <v>130175794</v>
       </c>
       <c r="B5" t="n">
-        <v>92484</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518227</v>
+        <v>518300</v>
       </c>
       <c r="R5" t="n">
-        <v>7206436</v>
+        <v>7206131</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,21 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1123,30 +1118,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130175786</v>
+        <v>130175785</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,7 +1153,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518241</v>
+        <v>518240</v>
       </c>
       <c r="R6" t="n">
         <v>7206479</v>
@@ -1210,21 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1241,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130175784</v>
+        <v>130175793</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518236</v>
+        <v>518299</v>
       </c>
       <c r="R7" t="n">
-        <v>7206497</v>
+        <v>7206131</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130175777</v>
+        <v>130175782</v>
       </c>
       <c r="B8" t="n">
-        <v>91781</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,30 +1343,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Genmyran, Kultsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518254</v>
+        <v>518218</v>
       </c>
       <c r="R8" t="n">
-        <v>7206369</v>
+        <v>7206465</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,323 +1441,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>130175785</v>
-      </c>
-      <c r="B9" t="n">
-        <v>79211</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Genmyran, Kultsjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>518240</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7206479</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>130175793</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79211</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Genmyran, Kultsjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>518299</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7206131</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>130175789</v>
-      </c>
-      <c r="B11" t="n">
-        <v>91781</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Genmyran, Kultsjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>518349</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7206204</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
